--- a/templates/SolidPro_CC_Owner_Mapping_Template.xlsx
+++ b/templates/SolidPro_CC_Owner_Mapping_Template.xlsx
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="27">
   <si>
     <t>CC_Code</t>
   </si>
@@ -74,6 +74,45 @@
     <t>BU_Head_Email</t>
   </si>
   <si>
+    <t>SolidPro Cost Centre Portal — Owner Mapping template</t>
+  </si>
+  <si>
+    <t>Enter your rows on the "Owner_Mapping" sheet under the header row. Keep the header row unchanged. The upload is rejected as a whole if any row has an error.</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>Required</t>
+  </si>
+  <si>
+    <t>Rule</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Must exist in the master and be Active</t>
+  </si>
+  <si>
+    <t>Full name of the accountable owner</t>
+  </si>
+  <si>
+    <t>Company email (allowed SolidPro domain only)</t>
+  </si>
+  <si>
+    <t>Company email; must differ from the owner</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Company email of the BU head</t>
+  </si>
+  <si>
+    <t>Example rows (for illustration only — do not copy blindly)</t>
+  </si>
+  <si>
     <t>IN-ENG-101</t>
   </si>
   <si>
@@ -99,49 +138,13 @@
   </si>
   <si>
     <t>nisha.r@solidpro-es.com</t>
-  </si>
-  <si>
-    <t>SolidPro Cost Centre Portal — Owner Mapping template</t>
-  </si>
-  <si>
-    <t>Replace the example rows on the first sheet. Keep the header row unchanged. The upload is rejected as a whole if any row has an error.</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Required</t>
-  </si>
-  <si>
-    <t>Rule</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Must exist in the master and be Active</t>
-  </si>
-  <si>
-    <t>Full name of the accountable owner</t>
-  </si>
-  <si>
-    <t>Company email (allowed SolidPro domain only)</t>
-  </si>
-  <si>
-    <t>Company email; must differ from the owner</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Company email of the BU head</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -161,6 +164,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16469D"/>
     </font>
   </fonts>
   <fills count="3">
@@ -188,13 +195,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="16" style="1" customWidth="1"/>
@@ -560,40 +568,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -603,7 +577,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -613,23 +587,23 @@
   <sheetData>
     <row r="1" spans="1:1" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -637,10 +611,10 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -648,10 +622,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -659,10 +633,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -670,10 +644,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -681,10 +655,66 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C14" t="s">
         <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
